--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{99FC725A-2F14-49DE-B4F8-5E6826124926}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE10896C-4253-4AA7-894F-8475DA1A5A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -460,32 +460,28 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>2026年8月31日-2026年9月4日</t>
+    <t>2026年9月7日-2026年9月11日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 学习了DataArts Studio资源迁移的全过程 以及约束条件 迁移选择的工具等
-2. 学习DataArts Studio支持的数据源包括哪些 以及连接参数怎么写
+1. 学习了数据集成的进阶操作 学习了增量迁移的原理介绍 以及四种增量迁移方式: 文件 关系数据库 HBase/CloudTable和MongoDB/DDS增量迁移
+2. 学习了时间宏变量使用解析
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-学习数据集成CDM如何离线作业
+学习如何优化迁移性能章节
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月4日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>周一:
-1. 学习了GDC的基本功能 对GDC有了初步的了解 
-2. 学习GDC数据迁移的产品文档中迁移相关的章节 并且仔细学习了一个GDC数据迁移的使用案例
+1. 学习了数据集成的进阶操作 学习了增量迁移的原理介绍 以及四种增量迁移方式: 文件 关系数据库 HBase/CloudTable和MongoDB/DDS增量迁移
+2. 学习了时间宏变量使用解析
 周二:
 1. 在大唐机房做了验收指南中的租户与VDC中的创建租户 VDC 创建VDC管理员等等 还有运维管理中的资源回收站 告警处理 运维监控等测试
 周三:
@@ -495,6 +491,10 @@
 周五:
 1. 学习了DataArts Studio资源迁移的全过程 以及约束条件 迁移选择的工具等 使用OBS桶或者将作业 配置和脚本等压缩成zip文件导出到本地 然后在新的工作空间导入
 2. 学习DataArts Studio支持的数据源包括哪些 以及连接参数怎么写</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作&amp;学习日报-9月7日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1228,6 +1228,93 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1281,97 +1368,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2122,7 +2122,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="47"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="47"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="58"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="45" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="A6" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="53"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,82 +2429,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2514,6 +2497,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DE10896C-4253-4AA7-894F-8475DA1A5A2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A36BA4D-87C8-4FEA-8A87-C28D84A2704E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -464,16 +464,20 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>工作&amp;学习日报-9月8日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>重点工作: 
-1. 学习了数据集成的进阶操作 学习了增量迁移的原理介绍 以及四种增量迁移方式: 文件 关系数据库 HBase/CloudTable和MongoDB/DDS增量迁移
-2. 学习了时间宏变量使用解析
+进行dgc验收测试指南里内容的测试
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-学习如何优化迁移性能章节
+1. 学习了DataArts Studio的实例发放和工作空间资源划分的实践操作 包含了如何表行数和库大小 通过数据质量对比迁移前后的结果
+以及如何处理数据开发中的告警
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -483,7 +487,7 @@
 1. 学习了数据集成的进阶操作 学习了增量迁移的原理介绍 以及四种增量迁移方式: 文件 关系数据库 HBase/CloudTable和MongoDB/DDS增量迁移
 2. 学习了时间宏变量使用解析
 周二:
-1. 在大唐机房做了验收指南中的租户与VDC中的创建租户 VDC 创建VDC管理员等等 还有运维管理中的资源回收站 告警处理 运维监控等测试
+1. 学习了DataArts Studio的实例发放和工作空间资源划分的实践操作 包含了如何表行数和库大小 通过数据质量对比迁移前后的结果以及如何处理数据开发中的告警
 周三:
 1. 继续做了验收测试指南 包括单点CCAE FusionCare日常巡检 创建主门户 创建策略 以及弹性云服务器申请 注册镜像 以及各种云硬盘操作 以及对象存储服务的测试
 周四:
@@ -491,10 +495,6 @@
 周五:
 1. 学习了DataArts Studio资源迁移的全过程 以及约束条件 迁移选择的工具等 使用OBS桶或者将作业 配置和脚本等压缩成zip文件导出到本地 然后在新的工作空间导入
 2. 学习DataArts Studio支持的数据源包括哪些 以及连接参数怎么写</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作&amp;学习日报-9月7日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1228,37 +1228,141 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1285,130 +1389,26 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="166">
@@ -2121,74 +2121,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A1" s="65" t="s">
-        <v>40</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="18" t="s">
+        <v>37</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
-      <c r="A3" s="68" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="70"/>
+      <c r="A3" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
     </row>
     <row r="4" spans="1:8" ht="54.75" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="24" t="s">
         <v>38</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="73"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="62"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
+      <c r="A6" s="66" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,65 +2429,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="42"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2497,23 +2514,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A36BA4D-87C8-4FEA-8A87-C28D84A2704E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8B4B2E-BE42-4C79-99D4-C3C6174DA45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -464,20 +464,20 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月8日</t>
+    <t>工作&amp;学习日报-9月9日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-进行dgc验收测试指南里内容的测试
+1. 做了数据治理中心的验收测试文档 我主要干的是数据开发的测试 包括dws hive spark和主机连接的创建 还有配置管理 包括新建jar file archive 环境变量登资源
+2. 还有脚本开发 包括dws flink python spark hive shell脚本的测试 脚本目录的重命名 移动 删除等操作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 学习了DataArts Studio的实例发放和工作空间资源划分的实践操作 包含了如何表行数和库大小 通过数据质量对比迁移前后的结果
-以及如何处理数据开发中的告警
+进行数据治理验收测试
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -489,7 +489,8 @@
 周二:
 1. 学习了DataArts Studio的实例发放和工作空间资源划分的实践操作 包含了如何表行数和库大小 通过数据质量对比迁移前后的结果以及如何处理数据开发中的告警
 周三:
-1. 继续做了验收测试指南 包括单点CCAE FusionCare日常巡检 创建主门户 创建策略 以及弹性云服务器申请 注册镜像 以及各种云硬盘操作 以及对象存储服务的测试
+1. 1. 做了数据治理中心的验收测试文档 我主要干的是数据开发的测试 包括dws hive spark和主机连接的创建 还有配置管理 包括新建jar file archive 环境变量登资源
+2. 还有脚本开发 包括dws flink python spark hive shell脚本的测试 脚本目录的重命名 移动 删除等操作
 周四:
 1. 学习数据迁移过程 首先迁移DGC的脚本 配置和作业等内容然后使用DGC这个迁移工具 批量迁移MRS和DWS的数据
 周五:
@@ -1228,6 +1229,152 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1263,152 +1410,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="166">
@@ -2121,74 +2122,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
-      <c r="A3" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
+      <c r="A3" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:8" ht="54.75" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
-      <c r="A5" s="24" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="26"/>
+      <c r="A5" s="71" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2227,154 +2228,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2384,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2412,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="53"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,82 +2430,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2514,6 +2498,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CA8B4B2E-BE42-4C79-99D4-C3C6174DA45F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED9FAE7-DEAB-4CF7-BFAB-F1C54DA9986B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -464,20 +464,20 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月9日</t>
+    <t>工作&amp;学习日报-9月10日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 做了数据治理中心的验收测试文档 我主要干的是数据开发的测试 包括dws hive spark和主机连接的创建 还有配置管理 包括新建jar file archive 环境变量登资源
-2. 还有脚本开发 包括dws flink python spark hive shell脚本的测试 脚本目录的重命名 移动 删除等操作
+1. 进行数据治理的验收测试 主要做的是数据架构验收用例: 比如添加审核人 创建流程设计 导入 导出 删除 创建主题设计 还有概念模型的创建
+2. 进行了码表的创建 发布 导出 等工作 以及数仓分层 业务指标的创建 和创建时间限定
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-进行数据治理验收测试
+进行源端和CDM的网络连通测试
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -492,7 +492,8 @@
 1. 1. 做了数据治理中心的验收测试文档 我主要干的是数据开发的测试 包括dws hive spark和主机连接的创建 还有配置管理 包括新建jar file archive 环境变量登资源
 2. 还有脚本开发 包括dws flink python spark hive shell脚本的测试 脚本目录的重命名 移动 删除等操作
 周四:
-1. 学习数据迁移过程 首先迁移DGC的脚本 配置和作业等内容然后使用DGC这个迁移工具 批量迁移MRS和DWS的数据
+1. 1. 进行数据治理的验收测试 主要做的是数据架构验收用例: 比如添加审核人 创建流程设计 导入 导出 删除 创建主题设计 还有概念模型的创建
+2. 进行了码表的创建 发布 导出 等工作 以及数仓分层 业务指标的创建 和创建时间限定
 周五:
 1. 学习了DataArts Studio资源迁移的全过程 以及约束条件 迁移选择的工具等 使用OBS桶或者将作业 配置和脚本等压缩成zip文件导出到本地 然后在新的工作空间导入
 2. 学习DataArts Studio支持的数据源包括哪些 以及连接参数怎么写</t>
@@ -1229,37 +1230,105 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1286,93 +1355,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2228,154 +2229,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="47"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="58"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="45"/>
+      <c r="H3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="47"/>
+      <c r="H4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2384,17 +2385,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2412,15 +2413,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2430,65 +2431,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="42"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2498,23 +2516,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED9FAE7-DEAB-4CF7-BFAB-F1C54DA9986B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B29703-1045-4770-AA25-C17BE4118F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -464,20 +464,19 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月10日</t>
+    <t>工作&amp;学习日报-9月11日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 进行数据治理的验收测试 主要做的是数据架构验收用例: 比如添加审核人 创建流程设计 导入 导出 删除 创建主题设计 还有概念模型的创建
-2. 进行了码表的创建 发布 导出 等工作 以及数仓分层 业务指标的创建 和创建时间限定
+1. 进行了DGC数据服务里的default空间的api发布 和授权操作 以及源端和CDM集群的网络连通行测试
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-进行源端和CDM的网络连通测试
+1. 继续进行数据服务里的dt_sub_nmnt_prd这个工作空间的API的发布和授权操作 
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -495,8 +494,7 @@
 1. 1. 进行数据治理的验收测试 主要做的是数据架构验收用例: 比如添加审核人 创建流程设计 导入 导出 删除 创建主题设计 还有概念模型的创建
 2. 进行了码表的创建 发布 导出 等工作 以及数仓分层 业务指标的创建 和创建时间限定
 周五:
-1. 学习了DataArts Studio资源迁移的全过程 以及约束条件 迁移选择的工具等 使用OBS桶或者将作业 配置和脚本等压缩成zip文件导出到本地 然后在新的工作空间导入
-2. 学习DataArts Studio支持的数据源包括哪些 以及连接参数怎么写</t>
+1. 进行了DGC数据服务里的default空间的api发布 和授权操作 以及源端和CDM集群的网络连通行测试</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1230,6 +1228,93 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1283,97 +1368,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2229,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="47"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="47"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="58"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="45" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2385,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2413,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="53"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2431,82 +2429,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2516,6 +2497,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86B29703-1045-4770-AA25-C17BE4118F75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFBA145-E02F-4F47-9123-D25DEC80C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -460,31 +460,28 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>2026年9月7日-2026年9月11日</t>
+    <t>工作&amp;学习日报-9月14日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月11日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>重点工作: 
-1. 进行了DGC数据服务里的default空间的api发布 和授权操作 以及源端和CDM集群的网络连通行测试
+1. 进行了源端和CDM集群的网络连通行测试
+2. 进行了数据库到源端的连通性 并做了连接 包括oracle postgresql和DM数据库的连接
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 继续进行数据服务里的dt_sub_nmnt_prd这个工作空间的API的发布和授权操作 
+1. 学习DGC作业迁移的流程
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>周一:
-1. 学习了数据集成的进阶操作 学习了增量迁移的原理介绍 以及四种增量迁移方式: 文件 关系数据库 HBase/CloudTable和MongoDB/DDS增量迁移
-2. 学习了时间宏变量使用解析
+1. 进行了源端和CDM集群的网络连通行测试
+2. 进行了数据库到源端的连通性 并做了连接 包括oracle postgresql和DM数据库的连接
 周二:
 1. 学习了DataArts Studio的实例发放和工作空间资源划分的实践操作 包含了如何表行数和库大小 通过数据质量对比迁移前后的结果以及如何处理数据开发中的告警
 周三:
@@ -495,6 +492,10 @@
 2. 进行了码表的创建 发布 导出 等工作 以及数仓分层 业务指标的创建 和创建时间限定
 周五:
 1. 进行了DGC数据服务里的default空间的api发布 和授权操作 以及源端和CDM集群的网络连通行测试</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>2026年9月14日-2026年9月18日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1228,37 +1229,105 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1285,93 +1354,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2122,7 +2123,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
@@ -2146,7 +2147,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="68" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
@@ -2170,7 +2171,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -2227,154 +2228,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="47"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="19" t="s">
-        <v>36</v>
-      </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="H2" s="47" t="s">
+        <v>40</v>
+      </c>
+      <c r="I2" s="47"/>
+      <c r="J2" s="58"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="45"/>
+      <c r="H3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="47"/>
+      <c r="H4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="32" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
+      <c r="A6" s="54" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2384,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2412,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,65 +2430,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="42"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2497,23 +2515,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBFBA145-E02F-4F47-9123-D25DEC80C299}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA630952-545E-490A-A555-D63A5FCC7E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -460,20 +460,24 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月14日</t>
+    <t>2026年9月14日-2026年9月18日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>工作&amp;学习日报-9月15日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>重点工作: 
-1. 进行了源端和CDM集群的网络连通行测试
-2. 进行了数据库到源端的连通性 并做了连接 包括oracle postgresql和DM数据库的连接
+1. 进行了源端到cdm集群端的网络和端口测试
+2. 从运营面进入数据治理中心  选择工作空间 然后进入数据集成 把dgc里的作业导入到cdm中
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 学习DGC作业迁移的流程
+1. 继续进行dgc迁移工作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -483,7 +487,8 @@
 1. 进行了源端和CDM集群的网络连通行测试
 2. 进行了数据库到源端的连通性 并做了连接 包括oracle postgresql和DM数据库的连接
 周二:
-1. 学习了DataArts Studio的实例发放和工作空间资源划分的实践操作 包含了如何表行数和库大小 通过数据质量对比迁移前后的结果以及如何处理数据开发中的告警
+1. 进行了源端到cdm集群端的网络和端口测试
+2. 从运营面进入数据治理中心  选择工作空间 然后进入数据集成 把dgc里的作业导入到cdm中
 周三:
 1. 1. 做了数据治理中心的验收测试文档 我主要干的是数据开发的测试 包括dws hive spark和主机连接的创建 还有配置管理 包括新建jar file archive 环境变量登资源
 2. 还有脚本开发 包括dws flink python spark hive shell脚本的测试 脚本目录的重命名 移动 删除等操作
@@ -492,10 +497,6 @@
 2. 进行了码表的创建 发布 导出 等工作 以及数仓分层 业务指标的创建 和创建时间限定
 周五:
 1. 进行了DGC数据服务里的default空间的api发布 和授权操作 以及源端和CDM集群的网络连通行测试</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>2026年9月14日-2026年9月18日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1229,6 +1230,93 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1282,97 +1370,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2123,7 +2124,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
@@ -2147,7 +2148,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="68" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
@@ -2171,7 +2172,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="71" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -2228,154 +2229,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="47"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="47"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="47" t="s">
-        <v>40</v>
-      </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="58"/>
+      <c r="H2" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="45" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="54" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="A6" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2384,17 +2385,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2412,15 +2413,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="53"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2430,82 +2431,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2515,6 +2499,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA630952-545E-490A-A555-D63A5FCC7E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B4155A-E223-4220-BB6B-DEDF83FCB6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -464,20 +464,20 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月15日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>重点工作: 
-1. 进行了源端到cdm集群端的网络和端口测试
-2. 从运营面进入数据治理中心  选择工作空间 然后进入数据集成 把dgc里的作业导入到cdm中
+1. 继续进行dgc迁移工作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>工作&amp;学习日报-9月16日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>重点工作: 
-1. 继续进行dgc迁移工作
+1. 继续对不通的网络进行重新测试
+2. 学习dgc迁移的其他理论知识
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -490,8 +490,8 @@
 1. 进行了源端到cdm集群端的网络和端口测试
 2. 从运营面进入数据治理中心  选择工作空间 然后进入数据集成 把dgc里的作业导入到cdm中
 周三:
-1. 1. 做了数据治理中心的验收测试文档 我主要干的是数据开发的测试 包括dws hive spark和主机连接的创建 还有配置管理 包括新建jar file archive 环境变量登资源
-2. 还有脚本开发 包括dws flink python spark hive shell脚本的测试 脚本目录的重命名 移动 删除等操作
+1. 继续对不通的网络进行重新测试
+2. 学习dgc迁移的其他理论知识
 周四:
 1. 1. 进行数据治理的验收测试 主要做的是数据架构验收用例: 比如添加审核人 创建流程设计 导入 导出 删除 创建主题设计 还有概念模型的创建
 2. 进行了码表的创建 发布 导出 等工作 以及数仓分层 业务指标的创建 和创建时间限定
@@ -1230,37 +1230,105 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1287,93 +1355,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2124,7 +2124,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="71" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -2229,154 +2229,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="47"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="58"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="45"/>
+      <c r="H3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="47"/>
+      <c r="H4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2385,17 +2385,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2413,15 +2413,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2431,65 +2431,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="42"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2499,23 +2516,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30B4155A-E223-4220-BB6B-DEDF83FCB6CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064213B5-109D-41E4-BA2F-CF1DE7A30A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -464,20 +464,20 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>工作&amp;学习日报-9月17日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>重点工作: 
-1. 继续进行dgc迁移工作
+1. 从OBS下载数据开发的内容 然后导入到CDM里面
+2. 继续对不通的网络进行重新测试
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月16日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>重点工作: 
-1. 继续对不通的网络进行重新测试
-2. 学习dgc迁移的其他理论知识
+1. 继续进行dgc迁移工作和网络测试
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -493,8 +493,7 @@
 1. 继续对不通的网络进行重新测试
 2. 学习dgc迁移的其他理论知识
 周四:
-1. 1. 进行数据治理的验收测试 主要做的是数据架构验收用例: 比如添加审核人 创建流程设计 导入 导出 删除 创建主题设计 还有概念模型的创建
-2. 进行了码表的创建 发布 导出 等工作 以及数仓分层 业务指标的创建 和创建时间限定
+1. 从OBS下载数据开发的内容 然后导入到CDM里面
 周五:
 1. 进行了DGC数据服务里的default空间的api发布 和授权操作 以及源端和CDM集群的网络连通行测试</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1230,6 +1229,93 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1283,97 +1369,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2124,7 +2123,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
@@ -2148,7 +2147,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
@@ -2172,7 +2171,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="71" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -2229,154 +2228,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="47"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="47"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="58"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="45" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2385,17 +2384,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2413,15 +2412,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="53"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2431,82 +2430,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2516,6 +2498,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{064213B5-109D-41E4-BA2F-CF1DE7A30A98}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F9A475-D300-4161-8C90-7B39E57E6BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -469,15 +469,15 @@
   </si>
   <si>
     <t>重点工作: 
-1. 从OBS下载数据开发的内容 然后导入到CDM里面
-2. 继续对不通的网络进行重新测试
+1. 登录到大数据集群的后台 查看本地端和北京端的数据量大小 并进行统计增量
+2. 查看数据迁移的日志 统计迁移耗时 根据库的大小 计算速率
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 继续进行dgc迁移工作和网络测试
+1. 继续进行dgc迁移工作和MRS增量的迁移工作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -495,7 +495,8 @@
 周四:
 1. 从OBS下载数据开发的内容 然后导入到CDM里面
 周五:
-1. 进行了DGC数据服务里的default空间的api发布 和授权操作 以及源端和CDM集群的网络连通行测试</t>
+1. 登录到大数据集群的后台 查看本地端和北京端的数据量大小 并进行统计增量
+2. 查看数据迁移的日志 统计迁移耗时 根据库的大小 计算速率</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1229,37 +1230,105 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1286,93 +1355,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2228,154 +2229,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="47"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="58"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="45"/>
+      <c r="H3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="47"/>
+      <c r="H4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2384,17 +2385,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2412,15 +2413,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2430,65 +2431,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="42"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2498,23 +2516,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{19F9A475-D300-4161-8C90-7B39E57E6BF7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1DF769-0AE4-45F4-BB07-ACF7D84556D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -460,32 +460,32 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>2026年9月14日-2026年9月18日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作&amp;学习日报-9月17日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>重点工作: 
-1. 登录到大数据集群的后台 查看本地端和北京端的数据量大小 并进行统计增量
-2. 查看数据迁移的日志 统计迁移耗时 根据库的大小 计算速率
+1. 进行MRS的增量迁移和DGC的迁移
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>2026年9月20日-2026年9月24日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作&amp;学习日报-9月21日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>重点工作: 
-1. 继续进行dgc迁移工作和MRS增量的迁移工作
+1. 进行default工作空间的作业调度的启动和检查操作
+2. 对北京端和目的端的MRS增量数据的统计 并标明哪些增长较快 
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>周一:
-1. 进行了源端和CDM集群的网络连通行测试
-2. 进行了数据库到源端的连通性 并做了连接 包括oracle postgresql和DM数据库的连接
+1. 进行default工作空间的作业调度的启动和检查操作
+2. 对北京端和目的端的MRS增量数据的统计 并标明哪些增长较快
 周二:
 1. 进行了源端到cdm集群端的网络和端口测试
 2. 从运营面进入数据治理中心  选择工作空间 然后进入数据集成 把dgc里的作业导入到cdm中
@@ -2124,7 +2124,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
@@ -2148,7 +2148,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
@@ -2172,7 +2172,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="71" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -2261,7 +2261,7 @@
         <v>2</v>
       </c>
       <c r="H2" s="47" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="I2" s="47"/>
       <c r="J2" s="58"/>

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EC1DF769-0AE4-45F4-BB07-ACF7D84556D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C3BB47-E421-4483-BB29-A56CF4E7A3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -460,24 +460,23 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>2026年9月20日-2026年9月24日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>工作&amp;学习日报-9月22日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>重点工作: 
-1. 进行MRS的增量迁移和DGC的迁移
+1. 开会讨论 解决了CDM集群里作业启动慢的问题 主要是因为慢的集群位高版本的CDM 开启了一个参数 会消耗CPU的速度 关闭该参数即可
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>2026年9月20日-2026年9月24日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作&amp;学习日报-9月21日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>重点工作: 
-1. 进行default工作空间的作业调度的启动和检查操作
-2. 对北京端和目的端的MRS增量数据的统计 并标明哪些增长较快 
+1. 继续进行DGC和MRS迁移
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -487,8 +486,7 @@
 1. 进行default工作空间的作业调度的启动和检查操作
 2. 对北京端和目的端的MRS增量数据的统计 并标明哪些增长较快
 周二:
-1. 进行了源端到cdm集群端的网络和端口测试
-2. 从运营面进入数据治理中心  选择工作空间 然后进入数据集成 把dgc里的作业导入到cdm中
+1. 开会讨论 解决了CDM集群里作业启动慢的问题 主要是因为慢的集群位高版本的CDM 开启了一个参数 会消耗CPU的速度 关闭该参数即可
 周三:
 1. 继续对不通的网络进行重新测试
 2. 学习dgc迁移的其他理论知识
@@ -1230,6 +1228,93 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1283,97 +1368,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2124,7 +2122,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="65" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B1" s="65"/>
       <c r="C1" s="65"/>
@@ -2148,7 +2146,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="68" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
@@ -2172,7 +2170,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="71" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -2229,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="47"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="47"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="47" t="s">
-        <v>37</v>
-      </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="58"/>
+      <c r="H2" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="45" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="32" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2385,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2413,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="53"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2431,82 +2429,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2516,6 +2497,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6C3BB47-E421-4483-BB29-A56CF4E7A3A0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9159308B-081C-4F07-B411-BEEDD7837CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -469,14 +469,14 @@
   </si>
   <si>
     <t>重点工作: 
-1. 开会讨论 解决了CDM集群里作业启动慢的问题 主要是因为慢的集群位高版本的CDM 开启了一个参数 会消耗CPU的速度 关闭该参数即可
+1. 继续进行DGC和MRS迁移
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 继续进行DGC和MRS迁移
+1. 通过manage one运营面 登录DGC 进入到CDM数据集成里 统计不同工作空间里的各个集群的导入效率 筛查出不合格的例子
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -488,8 +488,7 @@
 周二:
 1. 开会讨论 解决了CDM集群里作业启动慢的问题 主要是因为慢的集群位高版本的CDM 开启了一个参数 会消耗CPU的速度 关闭该参数即可
 周三:
-1. 继续对不通的网络进行重新测试
-2. 学习dgc迁移的其他理论知识
+1. 通过manage one运营面 登录DGC 进入到CDM数据集成里 统计不同工作空间里的各个集群的导入效率 筛查出不合格的例子
 周四:
 1. 从OBS下载数据开发的内容 然后导入到CDM里面
 周五:
@@ -1228,37 +1227,105 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1285,93 +1352,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2146,7 +2145,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
@@ -2170,7 +2169,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="71" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -2227,154 +2226,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="47"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="58"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="45"/>
+      <c r="H3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="47"/>
+      <c r="H4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2382,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2410,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,65 +2428,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="42"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2497,23 +2513,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9159308B-081C-4F07-B411-BEEDD7837CBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9769B6DD-2FEC-4933-9738-628E810BB397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3818" yWindow="2048" windowWidth="16200" windowHeight="9307" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -464,19 +464,20 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月22日</t>
+    <t>工作&amp;学习日报-9月24日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 继续进行DGC和MRS迁移
+1. 登录大数据的集群后台 分别查看北京和乌兰察布端数据同步情况 并做出总计
+2. 学习NTP时钟源调整的产品文档 并书写方案
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 通过manage one运营面 登录DGC 进入到CDM数据集成里 统计不同工作空间里的各个集群的导入效率 筛查出不合格的例子
+1. 继续进行DGC和MRS迁移和产品文档的学习
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -490,10 +491,10 @@
 周三:
 1. 通过manage one运营面 登录DGC 进入到CDM数据集成里 统计不同工作空间里的各个集群的导入效率 筛查出不合格的例子
 周四:
-1. 从OBS下载数据开发的内容 然后导入到CDM里面
+1. 登录大数据的集群后台 分别查看北京和乌兰察布端数据同步情况 并做出总计
+2. 学习NTP时钟源调整的产品文档 并书写方案
 周五:
-1. 登录到大数据集群的后台 查看本地端和北京端的数据量大小 并进行统计增量
-2. 查看数据迁移的日志 统计迁移耗时 根据库的大小 计算速率</t>
+无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1227,6 +1228,42 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1372,42 +1409,6 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="166">
@@ -2120,74 +2121,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
-      <c r="A3" s="68" t="s">
-        <v>39</v>
-      </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="70"/>
+      <c r="A3" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
     </row>
     <row r="4" spans="1:8" ht="54.75" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
-      <c r="A5" s="71" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="73"/>
+      <c r="A5" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="62"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2226,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="47"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="47"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="58"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="45" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="54" t="s">
+      <c r="A6" s="66" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2382,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2410,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2428,62 +2429,62 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9769B6DD-2FEC-4933-9738-628E810BB397}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC94A1CF-C3F4-4953-96D3-7D852F87A213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3818" yWindow="2048" windowWidth="16200" windowHeight="9307" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -469,14 +469,6 @@
   </si>
   <si>
     <t>重点工作: 
-1. 登录大数据的集群后台 分别查看北京和乌兰察布端数据同步情况 并做出总计
-2. 学习NTP时钟源调整的产品文档 并书写方案
-重大风险: 无 
-周边求助: 无</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>重点工作: 
 1. 继续进行DGC和MRS迁移和产品文档的学习
 重大风险: 无 
 周边求助: 无</t>
@@ -495,6 +487,14 @@
 2. 学习NTP时钟源调整的产品文档 并书写方案
 周五:
 无</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>重点工作: 
+1. 登录大数据的集群后台 分别查看北京和乌兰察布端数据同步情况 并做出总计
+2. 学习NTP时钟源调整的产品文档 并进行方案的书写
+重大风险: 无 
+周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1228,6 +1228,152 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1263,152 +1409,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="166">
@@ -2121,74 +2121,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
-      <c r="A3" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
+      <c r="A3" s="68" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:8" ht="54.75" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
-      <c r="A5" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="26"/>
+      <c r="A5" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="A6" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="53"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,82 +2429,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2514,6 +2497,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC94A1CF-C3F4-4953-96D3-7D852F87A213}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37BCA22-2947-4669-881E-7EC5C55A8A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4493" yWindow="2723" windowWidth="16200" windowHeight="9307" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -464,10 +464,6 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月24日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>重点工作: 
 1. 继续进行DGC和MRS迁移和产品文档的学习
 重大风险: 无 
@@ -490,9 +486,12 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>工作&amp;学习日报-9月28日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>重点工作: 
-1. 登录大数据的集群后台 分别查看北京和乌兰察布端数据同步情况 并做出总计
-2. 学习NTP时钟源调整的产品文档 并进行方案的书写
+1. 根据最新的分区表 做目的端 和源端数据一致性校验
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1228,37 +1227,141 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1285,130 +1388,26 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="166">
@@ -2121,74 +2120,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A1" s="65" t="s">
-        <v>37</v>
-      </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="A1" s="18" t="s">
+        <v>39</v>
+      </c>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
     </row>
     <row r="4" spans="1:8" ht="54.75" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
-      <c r="A5" s="71" t="s">
-        <v>38</v>
-      </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="73"/>
+      <c r="A5" s="24" t="s">
+        <v>37</v>
+      </c>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="62"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2227,154 +2226,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="32" t="s">
-        <v>39</v>
-      </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
+      <c r="A6" s="66" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2382,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2410,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,65 +2428,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="42"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2497,23 +2513,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A37BCA22-2947-4669-881E-7EC5C55A8A19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B83F5F7-03C4-4B3F-9FE1-6B66D94809FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4493" yWindow="2723" windowWidth="16200" windowHeight="9307" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -464,8 +464,20 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
+    <t>工作&amp;学习日报-9月29日</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
     <t>重点工作: 
-1. 继续进行DGC和MRS迁移和产品文档的学习
+1. 学习了使用华为一站式迁移工具进行DWS里的数据库的数据一致性 元数据 以及校验结果导出的流程
+2. 登录CDM后台 查看数据库的数据库名 状态 以及更新时间等
+重大风险: 无 
+周边求助: 无</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>重点工作: 
+1. 机房现场进行支持以及DWS的对数结果统计
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -475,7 +487,8 @@
 1. 进行default工作空间的作业调度的启动和检查操作
 2. 对北京端和目的端的MRS增量数据的统计 并标明哪些增长较快
 周二:
-1. 开会讨论 解决了CDM集群里作业启动慢的问题 主要是因为慢的集群位高版本的CDM 开启了一个参数 会消耗CPU的速度 关闭该参数即可
+1. 学习了使用华为一站式迁移工具进行DWS里的数据库的数据一致性 元数据 以及校验结果导出的流程
+2. 登录CDM后台 查看数据库的数据库名 状态 以及更新时间等
 周三:
 1. 通过manage one运营面 登录DGC 进入到CDM数据集成里 统计不同工作空间里的各个集群的导入效率 筛查出不合格的例子
 周四:
@@ -483,17 +496,6 @@
 2. 学习NTP时钟源调整的产品文档 并书写方案
 周五:
 无</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>工作&amp;学习日报-9月28日</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>重点工作: 
-1. 根据最新的分区表 做目的端 和源端数据一致性校验
-重大风险: 无 
-周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1263,6 +1265,93 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1316,97 +1405,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2121,7 +2123,7 @@
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
       <c r="A1" s="18" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B1" s="18"/>
       <c r="C1" s="18"/>
@@ -2145,7 +2147,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2169,7 +2171,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -2226,154 +2228,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="36"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="A6" s="44" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2382,17 +2384,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2410,15 +2412,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="65"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2428,82 +2430,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2513,6 +2498,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B83F5F7-03C4-4B3F-9FE1-6B66D94809FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D629B602-A94C-4D8D-8DC0-CE0E8080ED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -464,20 +464,20 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>工作&amp;学习日报-9月29日</t>
+    <t>工作&amp;学习日报-9月30日</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 学习了使用华为一站式迁移工具进行DWS里的数据库的数据一致性 元数据 以及校验结果导出的流程
-2. 登录CDM后台 查看数据库的数据库名 状态 以及更新时间等
+1. 进行DWS元数据核查和一致性校验 并导出迁移报告
+2. 编写脚本 进入CDM集群后台 查看数据库的运行状态 名称 以及数据更新时间等
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 机房现场进行支持以及DWS的对数结果统计
+1. 无
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -490,10 +490,10 @@
 1. 学习了使用华为一站式迁移工具进行DWS里的数据库的数据一致性 元数据 以及校验结果导出的流程
 2. 登录CDM后台 查看数据库的数据库名 状态 以及更新时间等
 周三:
-1. 通过manage one运营面 登录DGC 进入到CDM数据集成里 统计不同工作空间里的各个集群的导入效率 筛查出不合格的例子
+1. 进行DWS元数据核查和一致性校验 并导出迁移报告
+2. 编写脚本 进入CDM集群后台 查看数据库的运行状态 名称 以及数据更新时间等
 周四:
-1. 登录大数据的集群后台 分别查看北京和乌兰察布端数据同步情况 并做出总计
-2. 学习NTP时钟源调整的产品文档 并书写方案
+无
 周五:
 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1229,6 +1229,152 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1264,152 +1410,6 @@
     </xf>
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="166">
@@ -2122,74 +2122,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="65" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
-      <c r="F1" s="18"/>
-      <c r="G1" s="18"/>
-      <c r="H1" s="18"/>
+      <c r="B1" s="65"/>
+      <c r="C1" s="65"/>
+      <c r="D1" s="65"/>
+      <c r="E1" s="65"/>
+      <c r="F1" s="65"/>
+      <c r="G1" s="65"/>
+      <c r="H1" s="65"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="66" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="20"/>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
-      <c r="F2" s="20"/>
-      <c r="G2" s="20"/>
-      <c r="H2" s="20"/>
+      <c r="B2" s="67"/>
+      <c r="C2" s="67"/>
+      <c r="D2" s="67"/>
+      <c r="E2" s="67"/>
+      <c r="F2" s="67"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="67"/>
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="68" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="22"/>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="22"/>
-      <c r="G3" s="22"/>
-      <c r="H3" s="23"/>
+      <c r="B3" s="69"/>
+      <c r="C3" s="69"/>
+      <c r="D3" s="69"/>
+      <c r="E3" s="69"/>
+      <c r="F3" s="69"/>
+      <c r="G3" s="69"/>
+      <c r="H3" s="70"/>
     </row>
     <row r="4" spans="1:8" ht="54.75" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="A4" s="66" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="20"/>
-      <c r="C4" s="20"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="20"/>
-      <c r="F4" s="20"/>
-      <c r="G4" s="20"/>
-      <c r="H4" s="20"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="71" t="s">
         <v>39</v>
       </c>
-      <c r="B5" s="25"/>
-      <c r="C5" s="25"/>
-      <c r="D5" s="25"/>
-      <c r="E5" s="25"/>
-      <c r="F5" s="25"/>
-      <c r="G5" s="25"/>
-      <c r="H5" s="26"/>
+      <c r="B5" s="72"/>
+      <c r="C5" s="72"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="73"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="17"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="63"/>
+      <c r="D6" s="63"/>
+      <c r="E6" s="63"/>
+      <c r="F6" s="63"/>
+      <c r="G6" s="63"/>
+      <c r="H6" s="64"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2228,154 +2228,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="56"/>
+      <c r="C1" s="56"/>
+      <c r="D1" s="56"/>
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
+      <c r="J1" s="57"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="46" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="47"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="46" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="47"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="47" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="I2" s="47"/>
+      <c r="J2" s="58"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="46" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="47"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="45" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34" t="s">
+      <c r="G3" s="45"/>
+      <c r="H3" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="36"/>
+      <c r="I3" s="60"/>
+      <c r="J3" s="61"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="30" t="s">
+      <c r="B4" s="45"/>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="45"/>
+      <c r="F4" s="46" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38" t="s">
+      <c r="G4" s="47"/>
+      <c r="H4" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="I4" s="49"/>
+      <c r="J4" s="50"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="51" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="B5" s="52"/>
+      <c r="C5" s="52"/>
+      <c r="D5" s="52"/>
+      <c r="E5" s="52"/>
+      <c r="F5" s="52"/>
+      <c r="G5" s="52"/>
+      <c r="H5" s="52"/>
+      <c r="I5" s="52"/>
+      <c r="J5" s="53"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="54" t="s">
         <v>40</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="40"/>
+      <c r="C6" s="40"/>
+      <c r="D6" s="40"/>
+      <c r="E6" s="40"/>
+      <c r="F6" s="40"/>
+      <c r="G6" s="40"/>
+      <c r="H6" s="40"/>
+      <c r="I6" s="40"/>
+      <c r="J6" s="41"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="B7" s="37"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="37"/>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="39" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="B8" s="40"/>
+      <c r="C8" s="40"/>
+      <c r="D8" s="40"/>
+      <c r="E8" s="40"/>
+      <c r="F8" s="40"/>
+      <c r="G8" s="40"/>
+      <c r="H8" s="40"/>
+      <c r="I8" s="40"/>
+      <c r="J8" s="41"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="B9" s="37"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="37"/>
+      <c r="F9" s="37"/>
+      <c r="G9" s="37"/>
+      <c r="H9" s="37"/>
+      <c r="I9" s="37"/>
+      <c r="J9" s="38"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2384,17 +2384,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="42" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="43"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="32" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="34"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2412,15 +2412,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="23" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="24"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="65"/>
+      <c r="G11" s="25"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2430,65 +2430,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="68"/>
+      <c r="B12" s="27"/>
+      <c r="C12" s="27"/>
+      <c r="D12" s="27"/>
+      <c r="E12" s="27"/>
+      <c r="F12" s="27"/>
+      <c r="G12" s="27"/>
+      <c r="H12" s="27"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="28"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="53" t="s">
+      <c r="C13" s="30"/>
+      <c r="D13" s="31"/>
+      <c r="E13" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="54"/>
+      <c r="F13" s="33"/>
+      <c r="G13" s="34"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="32" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="73"/>
+      <c r="J13" s="35"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58" t="s">
+      <c r="C14" s="16"/>
+      <c r="D14" s="17"/>
+      <c r="E14" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="20"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="62"/>
+      <c r="J14" s="22"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2498,23 +2515,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D629B602-A94C-4D8D-8DC0-CE0E8080ED5F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE98616-7145-4EA0-9A8E-945BF5B50643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -468,21 +468,6 @@
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
-    <t>重点工作: 
-1. 进行DWS元数据核查和一致性校验 并导出迁移报告
-2. 编写脚本 进入CDM集群后台 查看数据库的运行状态 名称 以及数据更新时间等
-重大风险: 无 
-周边求助: 无</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>重点工作: 
-1. 无
-重大风险: 无 
-周边求助: 无</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
     <t>周一:
 1. 进行default工作空间的作业调度的启动和检查操作
 2. 对北京端和目的端的MRS增量数据的统计 并标明哪些增长较快
@@ -496,6 +481,23 @@
 无
 周五:
 无</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>重点工作: 
+1. 对DWS相关数据进行日常核查，关注数据更新情况及数据一致性
+2. 查看CDM集群相关脚本及数据库运行状态，梳理日常检查项
+3. 整理前期数据核查内容，熟悉相关表结构及数据校验流程
+重大风险: 无 
+周边求助: 无</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>重点工作: 
+1. 熟悉DWS数据核查及一致性校验相关流程，梳理日常检查内容
+2. 回顾CDM集群脚本及数据库运行状态检查相关事项，为后续核查工作做准备
+重大风险: 无 
+周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1229,6 +1231,93 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1282,97 +1371,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2147,7 +2149,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="68" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B3" s="69"/>
       <c r="C3" s="69"/>
@@ -2171,7 +2173,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="71" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="72"/>
       <c r="C5" s="72"/>
@@ -2228,154 +2230,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="15" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="56"/>
-      <c r="C1" s="56"/>
-      <c r="D1" s="56"/>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="56"/>
-      <c r="H1" s="56"/>
-      <c r="I1" s="56"/>
-      <c r="J1" s="57"/>
+      <c r="B1" s="16"/>
+      <c r="C1" s="16"/>
+      <c r="D1" s="16"/>
+      <c r="E1" s="16"/>
+      <c r="F1" s="16"/>
+      <c r="G1" s="16"/>
+      <c r="H1" s="16"/>
+      <c r="I1" s="16"/>
+      <c r="J1" s="17"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="46" t="s">
+      <c r="B2" s="18" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="47"/>
+      <c r="C2" s="19"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="46" t="s">
+      <c r="E2" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="47"/>
+      <c r="F2" s="19"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="47" t="s">
+      <c r="H2" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="47"/>
-      <c r="J2" s="58"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="20"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="46" t="s">
+      <c r="B3" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="47"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="45" t="s">
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="21" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="45"/>
-      <c r="H3" s="59" t="s">
+      <c r="G3" s="21"/>
+      <c r="H3" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="60"/>
-      <c r="J3" s="61"/>
+      <c r="I3" s="23"/>
+      <c r="J3" s="24"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="25" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="45"/>
-      <c r="C4" s="45"/>
-      <c r="D4" s="45"/>
-      <c r="E4" s="45"/>
-      <c r="F4" s="46" t="s">
+      <c r="B4" s="21"/>
+      <c r="C4" s="21"/>
+      <c r="D4" s="21"/>
+      <c r="E4" s="21"/>
+      <c r="F4" s="18" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="47"/>
-      <c r="H4" s="48" t="s">
+      <c r="G4" s="19"/>
+      <c r="H4" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="49"/>
-      <c r="J4" s="50"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="28"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="51" t="s">
+      <c r="A5" s="29" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="52"/>
-      <c r="C5" s="52"/>
-      <c r="D5" s="52"/>
-      <c r="E5" s="52"/>
-      <c r="F5" s="52"/>
-      <c r="G5" s="52"/>
-      <c r="H5" s="52"/>
-      <c r="I5" s="52"/>
-      <c r="J5" s="53"/>
+      <c r="B5" s="30"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="30"/>
+      <c r="H5" s="30"/>
+      <c r="I5" s="30"/>
+      <c r="J5" s="31"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="54" t="s">
-        <v>40</v>
-      </c>
-      <c r="B6" s="40"/>
-      <c r="C6" s="40"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="40"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="40"/>
-      <c r="H6" s="40"/>
-      <c r="I6" s="40"/>
-      <c r="J6" s="41"/>
+      <c r="A6" s="32" t="s">
+        <v>38</v>
+      </c>
+      <c r="B6" s="33"/>
+      <c r="C6" s="33"/>
+      <c r="D6" s="33"/>
+      <c r="E6" s="33"/>
+      <c r="F6" s="33"/>
+      <c r="G6" s="33"/>
+      <c r="H6" s="33"/>
+      <c r="I6" s="33"/>
+      <c r="J6" s="34"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="36" t="s">
+      <c r="A7" s="35" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="37"/>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
-      <c r="F7" s="37"/>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
-      <c r="I7" s="37"/>
-      <c r="J7" s="38"/>
+      <c r="B7" s="36"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="36"/>
+      <c r="E7" s="36"/>
+      <c r="F7" s="36"/>
+      <c r="G7" s="36"/>
+      <c r="H7" s="36"/>
+      <c r="I7" s="36"/>
+      <c r="J7" s="37"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="39" t="s">
+      <c r="A8" s="38" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="40"/>
-      <c r="C8" s="40"/>
-      <c r="D8" s="40"/>
-      <c r="E8" s="40"/>
-      <c r="F8" s="40"/>
-      <c r="G8" s="40"/>
-      <c r="H8" s="40"/>
-      <c r="I8" s="40"/>
-      <c r="J8" s="41"/>
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="33"/>
+      <c r="F8" s="33"/>
+      <c r="G8" s="33"/>
+      <c r="H8" s="33"/>
+      <c r="I8" s="33"/>
+      <c r="J8" s="34"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="36" t="s">
+      <c r="A9" s="35" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="37"/>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="37"/>
-      <c r="F9" s="37"/>
-      <c r="G9" s="37"/>
-      <c r="H9" s="37"/>
-      <c r="I9" s="37"/>
-      <c r="J9" s="38"/>
+      <c r="B9" s="36"/>
+      <c r="C9" s="36"/>
+      <c r="D9" s="36"/>
+      <c r="E9" s="36"/>
+      <c r="F9" s="36"/>
+      <c r="G9" s="36"/>
+      <c r="H9" s="36"/>
+      <c r="I9" s="36"/>
+      <c r="J9" s="37"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2384,17 +2386,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="42" t="s">
+      <c r="C10" s="39" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="43"/>
+      <c r="D10" s="40"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="32" t="s">
+      <c r="F10" s="41" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="34"/>
+      <c r="G10" s="42"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2412,15 +2414,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="51" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="24"/>
+      <c r="D11" s="52"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="21" t="s">
+      <c r="F11" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="25"/>
+      <c r="G11" s="53"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2430,82 +2432,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="26" t="s">
+      <c r="A12" s="54" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="27"/>
-      <c r="C12" s="27"/>
-      <c r="D12" s="27"/>
-      <c r="E12" s="27"/>
-      <c r="F12" s="27"/>
-      <c r="G12" s="27"/>
-      <c r="H12" s="27"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="28"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="55"/>
+      <c r="D12" s="55"/>
+      <c r="E12" s="55"/>
+      <c r="F12" s="55"/>
+      <c r="G12" s="55"/>
+      <c r="H12" s="55"/>
+      <c r="I12" s="55"/>
+      <c r="J12" s="56"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="29" t="s">
+      <c r="B13" s="57" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="30"/>
-      <c r="D13" s="31"/>
-      <c r="E13" s="32" t="s">
+      <c r="C13" s="58"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="41" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="33"/>
-      <c r="G13" s="34"/>
+      <c r="F13" s="60"/>
+      <c r="G13" s="42"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="32" t="s">
+      <c r="I13" s="41" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="35"/>
+      <c r="J13" s="61"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="15" t="s">
+      <c r="B14" s="43" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="16"/>
-      <c r="D14" s="17"/>
-      <c r="E14" s="18" t="s">
+      <c r="C14" s="44"/>
+      <c r="D14" s="45"/>
+      <c r="E14" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="19"/>
-      <c r="G14" s="20"/>
+      <c r="F14" s="47"/>
+      <c r="G14" s="48"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="I14" s="49" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="22"/>
+      <c r="J14" s="50"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2515,6 +2500,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EBE98616-7145-4EA0-9A8E-945BF5B50643}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B46D57C-1C01-4D1B-A7C6-E046E5887FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,17 +485,15 @@
   </si>
   <si>
     <t>重点工作: 
-1. 对DWS相关数据进行日常核查，关注数据更新情况及数据一致性
-2. 查看CDM集群相关脚本及数据库运行状态，梳理日常检查项
-3. 整理前期数据核查内容，熟悉相关表结构及数据校验流程
+1. 进行DWS相关数据核对，检查数据是否一致
+2. 对部分数据字段及数据更新情况进行检查
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 熟悉DWS数据核查及一致性校验相关流程，梳理日常检查内容
-2. 回顾CDM集群脚本及数据库运行状态检查相关事项，为后续核查工作做准备
+1. 继续进行DWS相关数据核对及一致性检查
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1231,37 +1229,141 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1288,130 +1390,26 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="166">
@@ -2124,74 +2122,74 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="22.5" customHeight="1">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="18" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="H1" s="65"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="20.25" customHeight="1">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="67"/>
-      <c r="C2" s="67"/>
-      <c r="D2" s="67"/>
-      <c r="E2" s="67"/>
-      <c r="F2" s="67"/>
-      <c r="G2" s="67"/>
-      <c r="H2" s="67"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
-      <c r="A3" s="68" t="s">
+      <c r="A3" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="B3" s="69"/>
-      <c r="C3" s="69"/>
-      <c r="D3" s="69"/>
-      <c r="E3" s="69"/>
-      <c r="F3" s="69"/>
-      <c r="G3" s="69"/>
-      <c r="H3" s="70"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="23"/>
     </row>
     <row r="4" spans="1:8" ht="54.75" customHeight="1">
-      <c r="A4" s="66" t="s">
+      <c r="A4" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
-      <c r="F4" s="67"/>
-      <c r="G4" s="67"/>
-      <c r="H4" s="67"/>
+      <c r="B4" s="20"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="20"/>
+      <c r="F4" s="20"/>
+      <c r="G4" s="20"/>
+      <c r="H4" s="20"/>
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
-      <c r="A5" s="71" t="s">
+      <c r="A5" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="B5" s="72"/>
-      <c r="C5" s="72"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="73"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="25"/>
+      <c r="D5" s="25"/>
+      <c r="E5" s="25"/>
+      <c r="F5" s="25"/>
+      <c r="G5" s="25"/>
+      <c r="H5" s="26"/>
     </row>
     <row r="6" spans="1:8" ht="14.25" customHeight="1">
-      <c r="A6" s="62"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="63"/>
-      <c r="D6" s="63"/>
-      <c r="E6" s="63"/>
-      <c r="F6" s="63"/>
-      <c r="G6" s="63"/>
-      <c r="H6" s="64"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -2230,154 +2228,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="17"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="18" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="19"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="18" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="19"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="19"/>
-      <c r="J2" s="20"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="21" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="21"/>
-      <c r="H3" s="22" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="23"/>
-      <c r="J3" s="24"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="21"/>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
-      <c r="F4" s="18" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="19"/>
-      <c r="H4" s="26" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="27"/>
-      <c r="J4" s="28"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="29" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="30"/>
-      <c r="C5" s="30"/>
-      <c r="D5" s="30"/>
-      <c r="E5" s="30"/>
-      <c r="F5" s="30"/>
-      <c r="G5" s="30"/>
-      <c r="H5" s="30"/>
-      <c r="I5" s="30"/>
-      <c r="J5" s="31"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="33"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="33"/>
-      <c r="E6" s="33"/>
-      <c r="F6" s="33"/>
-      <c r="G6" s="33"/>
-      <c r="H6" s="33"/>
-      <c r="I6" s="33"/>
-      <c r="J6" s="34"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="35" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="36"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="36"/>
-      <c r="E7" s="36"/>
-      <c r="F7" s="36"/>
-      <c r="G7" s="36"/>
-      <c r="H7" s="36"/>
-      <c r="I7" s="36"/>
-      <c r="J7" s="37"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="38" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="33"/>
-      <c r="F8" s="33"/>
-      <c r="G8" s="33"/>
-      <c r="H8" s="33"/>
-      <c r="I8" s="33"/>
-      <c r="J8" s="34"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="35" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="36"/>
-      <c r="C9" s="36"/>
-      <c r="D9" s="36"/>
-      <c r="E9" s="36"/>
-      <c r="F9" s="36"/>
-      <c r="G9" s="36"/>
-      <c r="H9" s="36"/>
-      <c r="I9" s="36"/>
-      <c r="J9" s="37"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2386,17 +2384,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="39" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="40"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="41" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="42"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2414,15 +2412,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="51" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="52"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="49" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="53"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2432,65 +2430,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="54" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="55"/>
-      <c r="C12" s="55"/>
-      <c r="D12" s="55"/>
-      <c r="E12" s="55"/>
-      <c r="F12" s="55"/>
-      <c r="G12" s="55"/>
-      <c r="H12" s="55"/>
-      <c r="I12" s="55"/>
-      <c r="J12" s="56"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="57" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="58"/>
-      <c r="D13" s="59"/>
-      <c r="E13" s="41" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="60"/>
-      <c r="G13" s="42"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="41" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="61"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="43" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="44"/>
-      <c r="D14" s="45"/>
-      <c r="E14" s="46" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="47"/>
-      <c r="G14" s="48"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="49" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="50"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2500,23 +2515,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B46D57C-1C01-4D1B-A7C6-E046E5887FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAA944F-E7C5-4ACB-B560-D4DD5FC66C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,15 +485,15 @@
   </si>
   <si>
     <t>重点工作: 
-1. 进行DWS相关数据核对，检查数据是否一致
-2. 对部分数据字段及数据更新情况进行检查
+1. 公司学习HCS8.2.1版本IAM证书替换和FusionSphere keystone PKI Token证书替换操作
+2. 学习替换后的验证操作等
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 继续进行DWS相关数据核对及一致性检查
+1. 继续学习证书替换知识
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1265,6 +1265,93 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1318,97 +1405,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2228,154 +2228,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="36"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2384,17 +2384,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2412,15 +2412,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="65"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2430,82 +2430,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2515,6 +2498,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{ECAA944F-E7C5-4ACB-B560-D4DD5FC66C37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26C7F2B-C97C-456F-B4C4-CB334504F47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,15 +485,14 @@
   </si>
   <si>
     <t>重点工作: 
-1. 公司学习HCS8.2.1版本IAM证书替换和FusionSphere keystone PKI Token证书替换操作
-2. 学习替换后的验证操作等
+1. 公司学习HCS8.5.1版本的Stack FusionSphere服务证书过期风险预警证书替换操作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 继续学习证书替换知识
+1. 继续学习Stack FusionSphere证书替换方案
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1265,37 +1264,105 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1322,93 +1389,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2228,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="36"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="30" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2384,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2412,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="65"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2430,65 +2429,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="68"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="53" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="54"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="73"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="62"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2498,23 +2514,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C26C7F2B-C97C-456F-B4C4-CB334504F47F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5A7460-B7B4-46B7-88DF-D11D0CF8E8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,14 +485,14 @@
   </si>
   <si>
     <t>重点工作: 
-1. 公司学习HCS8.5.1版本的Stack FusionSphere服务证书过期风险预警证书替换操作
+1. 继续学习Stack FusionSphere证书替换方案
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 继续学习Stack FusionSphere证书替换方案
+1. 公司学习HCS8.5.1版本的Stack FusionSphere API证书替换流程以及替换前检查操作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1264,6 +1264,93 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1317,97 +1404,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="36"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="65"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,82 +2429,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2514,6 +2497,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5A7460-B7B4-46B7-88DF-D11D0CF8E8A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D188EB6-988F-4680-9A8E-4CBFCA8F13CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,7 +492,7 @@
   </si>
   <si>
     <t>重点工作: 
-1. 公司学习HCS8.5.1版本的Stack FusionSphere API证书替换流程以及替换前检查操作
+1. 总结前段时间跟岗学习 大唐乌兰察布数据迁移项目的一些细节问题 以及需要总结改进的地方
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1264,37 +1264,105 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1321,93 +1389,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="36"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="30" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="65"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,65 +2429,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="68"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="53" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="54"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="73"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="62"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2497,23 +2514,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D188EB6-988F-4680-9A8E-4CBFCA8F13CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F888055-68ED-465F-B46F-FADCD5B0C68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,14 +485,14 @@
   </si>
   <si>
     <t>重点工作: 
-1. 继续学习Stack FusionSphere证书替换方案
+1. 办公室学习IAM证书替换和FusionSphere keystone PKI Token证书替换操作流程及信息收集内容
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 总结前段时间跟岗学习 大唐乌兰察布数据迁移项目的一些细节问题 以及需要总结改进的地方
+1. 联通机房蒙能云平台操作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1264,6 +1264,93 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1317,97 +1404,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="36"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="65"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,82 +2429,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2514,6 +2497,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F888055-68ED-465F-B46F-FADCD5B0C68E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF800D59-1BF6-4490-AF1E-D5646BD41797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,14 +485,14 @@
   </si>
   <si>
     <t>重点工作: 
-1. 办公室学习IAM证书替换和FusionSphere keystone PKI Token证书替换操作流程及信息收集内容
+1. 联通机房蒙能云平台操作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 联通机房蒙能云平台操作
+1. 蒙能云平台零信任测试虚拟机扩容操作 更改虚拟机规格和扩容磁盘 并进行文件系统挂载等操作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1264,37 +1264,105 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1321,93 +1389,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2146,7 +2146,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2170,7 +2170,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="36"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="30" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="65"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,65 +2429,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="68"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="53" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="54"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="73"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="62"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2497,23 +2514,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF800D59-1BF6-4490-AF1E-D5646BD41797}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9763BFDA-0D65-4933-8F4E-240AE38AE7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4493" yWindow="2723" windowWidth="16200" windowHeight="9307" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -492,7 +492,7 @@
   </si>
   <si>
     <t>重点工作: 
-1. 蒙能云平台零信任测试虚拟机扩容操作 更改虚拟机规格和扩容磁盘 并进行文件系统挂载等操作
+1. 蒙能云平台移动门户业务系统虚拟机的发放及系统盘扩容操作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1264,6 +1264,93 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1317,97 +1404,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="36"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="65"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,82 +2429,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2514,6 +2497,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9763BFDA-0D65-4933-8F4E-240AE38AE7DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1452DF-2453-4481-AFE3-EED8D45BC756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4493" yWindow="2723" windowWidth="16200" windowHeight="9307" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="1.日工作简报" sheetId="11" r:id="rId1"/>
@@ -492,7 +492,7 @@
   </si>
   <si>
     <t>重点工作: 
-1. 蒙能云平台移动门户业务系统虚拟机的发放及系统盘扩容操作
+1. 编写华为云Stack租户与云资源管理操作手册 在serviceom进行公共镜像的制作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -1264,37 +1264,105 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1321,93 +1389,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1763,9 +1763,9 @@
         </xdr:from>
         <xdr:to>
           <xdr:col>0</xdr:col>
-          <xdr:colOff>2176463</xdr:colOff>
+          <xdr:colOff>1638300</xdr:colOff>
           <xdr:row>6</xdr:row>
-          <xdr:rowOff>147638</xdr:rowOff>
+          <xdr:rowOff>104775</xdr:rowOff>
         </xdr:to>
         <xdr:sp macro="" textlink="">
           <xdr:nvSpPr>
@@ -2227,154 +2227,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="36"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="30" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2383,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2411,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="65"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,65 +2429,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="68"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="53" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="54"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="73"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="62"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2497,23 +2514,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">
@@ -2546,13 +2546,14 @@
   </sheetData>
   <phoneticPr fontId="30" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
-  <legacyDrawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+  <legacyDrawing r:id="rId3"/>
   <oleObjects>
     <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
       <mc:Choice Requires="x14">
-        <oleObject progId="Excel.Sheet.12" dvAspect="DVASPECT_ICON" shapeId="2049" r:id="rId3">
-          <objectPr defaultSize="0" r:id="rId4">
+        <oleObject progId="Excel.Sheet.12" dvAspect="DVASPECT_ICON" shapeId="2049" r:id="rId4">
+          <objectPr defaultSize="0" r:id="rId5">
             <anchor moveWithCells="1">
               <from>
                 <xdr:col>0</xdr:col>
@@ -2562,16 +2563,16 @@
               </from>
               <to>
                 <xdr:col>0</xdr:col>
-                <xdr:colOff>2176463</xdr:colOff>
+                <xdr:colOff>1638300</xdr:colOff>
                 <xdr:row>6</xdr:row>
-                <xdr:rowOff>147638</xdr:rowOff>
+                <xdr:rowOff>104775</xdr:rowOff>
               </to>
             </anchor>
           </objectPr>
         </oleObject>
       </mc:Choice>
       <mc:Fallback>
-        <oleObject progId="Excel.Sheet.12" dvAspect="DVASPECT_ICON" shapeId="2049" r:id="rId3"/>
+        <oleObject progId="Excel.Sheet.12" dvAspect="DVASPECT_ICON" shapeId="2049" r:id="rId4"/>
       </mc:Fallback>
     </mc:AlternateContent>
   </oleObjects>

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE1452DF-2453-4481-AFE3-EED8D45BC756}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D61E409-EAC2-4BDB-AA4E-2A512D621B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -492,7 +492,7 @@
   </si>
   <si>
     <t>重点工作: 
-1. 编写华为云Stack租户与云资源管理操作手册 在serviceom进行公共镜像的制作
+1. 整理蒙能云平台所需资料 并对其余业务系统进行网络测试
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D61E409-EAC2-4BDB-AA4E-2A512D621B54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769DA46F-C5C6-4C77-B827-656B01809100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,16 +485,18 @@
   </si>
   <si>
     <t>重点工作: 
-1. 联通机房蒙能云平台操作
+1. 辅助进行redis扩容操作已经不需要的租户里的资源清理操作
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
   <si>
     <t>重点工作: 
-1. 整理蒙能云平台所需资料 并对其余业务系统进行网络测试
+1. 联通机房蒙能云平台操作
 重大风险: 无 
-周边求助: 无</t>
+周边求助: 无
+周二: 继续redis扩容
+周三: 进行浮动ip的分配以及实现HA高可用</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1264,6 +1266,93 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1317,97 +1406,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2146,7 +2148,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2170,7 +2172,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -2227,154 +2229,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="36"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2383,17 +2385,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2411,15 +2413,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="65"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2429,82 +2431,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2514,6 +2499,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30527"/>
   <workbookPr updateLinks="never" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769DA46F-C5C6-4C77-B827-656B01809100}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558EDC86-A53F-4CDF-B795-449C6147FCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,7 +485,7 @@
   </si>
   <si>
     <t>重点工作: 
-1. 辅助进行redis扩容操作已经不需要的租户里的资源清理操作
+1. 蒙能进行redis扩容操作时遇到的大规格虚拟机无法创建问题的解决
 重大风险: 无 
 周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
@@ -495,8 +495,7 @@
 1. 联通机房蒙能云平台操作
 重大风险: 无 
 周边求助: 无
-周二: 继续redis扩容
-周三: 进行浮动ip的分配以及实现HA高可用</t>
+周三: 继续redis扩容</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1266,37 +1265,105 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1323,93 +1390,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2229,154 +2228,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="36"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="30" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2385,17 +2384,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2413,15 +2412,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="65"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2431,65 +2430,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="68"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="53" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="54"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="73"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="62"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2499,23 +2515,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{558EDC86-A53F-4CDF-B795-449C6147FCBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7A69E9-2573-4E26-ABE8-192B0C1B2AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,17 +485,19 @@
   </si>
   <si>
     <t>重点工作: 
-1. 蒙能进行redis扩容操作时遇到的大规格虚拟机无法创建问题的解决
-重大风险: 无 
-周边求助: 无</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>重点工作: 
 1. 联通机房蒙能云平台操作
 重大风险: 无 
 周边求助: 无
-周三: 继续redis扩容</t>
+周四: 在运营面测试创建obs和sfs 以及发放redis实例等操作</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>重点工作: 
+1. 解决obs对象存储创建时权限不足问题
+2. sfs文件系统无法创建 参数报错问题
+3. 理解sentinel集群的作用及如何发放redis实例等操作
+重大风险: 无 
+周边求助: 无</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1265,6 +1267,93 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1318,97 +1407,10 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2147,7 +2149,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2171,7 +2173,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -2228,154 +2230,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="67" t="s">
+      <c r="A1" s="27" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="68"/>
-      <c r="C1" s="68"/>
-      <c r="D1" s="68"/>
-      <c r="E1" s="68"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="68"/>
-      <c r="H1" s="68"/>
-      <c r="I1" s="68"/>
-      <c r="J1" s="69"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="29"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="58" t="s">
+      <c r="B2" s="30" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="59"/>
+      <c r="C2" s="31"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="58" t="s">
+      <c r="E2" s="30" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="59"/>
+      <c r="F2" s="31"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="59" t="s">
+      <c r="H2" s="31" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="59"/>
-      <c r="J2" s="70"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="30" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="59"/>
-      <c r="D3" s="59"/>
-      <c r="E3" s="59"/>
-      <c r="F3" s="57" t="s">
+      <c r="C3" s="31"/>
+      <c r="D3" s="31"/>
+      <c r="E3" s="31"/>
+      <c r="F3" s="33" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="71" t="s">
+      <c r="G3" s="33"/>
+      <c r="H3" s="34" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="72"/>
-      <c r="J3" s="73"/>
+      <c r="I3" s="35"/>
+      <c r="J3" s="36"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="56" t="s">
+      <c r="A4" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="57"/>
-      <c r="C4" s="57"/>
-      <c r="D4" s="57"/>
-      <c r="E4" s="57"/>
-      <c r="F4" s="58" t="s">
+      <c r="B4" s="33"/>
+      <c r="C4" s="33"/>
+      <c r="D4" s="33"/>
+      <c r="E4" s="33"/>
+      <c r="F4" s="30" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="59"/>
-      <c r="H4" s="60" t="s">
+      <c r="G4" s="31"/>
+      <c r="H4" s="38" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="61"/>
-      <c r="J4" s="62"/>
+      <c r="I4" s="39"/>
+      <c r="J4" s="40"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="63" t="s">
+      <c r="A5" s="41" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="64"/>
-      <c r="C5" s="64"/>
-      <c r="D5" s="64"/>
-      <c r="E5" s="64"/>
-      <c r="F5" s="64"/>
-      <c r="G5" s="64"/>
-      <c r="H5" s="64"/>
-      <c r="I5" s="64"/>
-      <c r="J5" s="65"/>
+      <c r="B5" s="42"/>
+      <c r="C5" s="42"/>
+      <c r="D5" s="42"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="42"/>
+      <c r="G5" s="42"/>
+      <c r="H5" s="42"/>
+      <c r="I5" s="42"/>
+      <c r="J5" s="43"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="66" t="s">
+      <c r="A6" s="44" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="52"/>
-      <c r="C6" s="52"/>
-      <c r="D6" s="52"/>
-      <c r="E6" s="52"/>
-      <c r="F6" s="52"/>
-      <c r="G6" s="52"/>
-      <c r="H6" s="52"/>
-      <c r="I6" s="52"/>
-      <c r="J6" s="53"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="45"/>
+      <c r="F6" s="45"/>
+      <c r="G6" s="45"/>
+      <c r="H6" s="45"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="46"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="48" t="s">
+      <c r="A7" s="47" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="49"/>
-      <c r="C7" s="49"/>
-      <c r="D7" s="49"/>
-      <c r="E7" s="49"/>
-      <c r="F7" s="49"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="49"/>
-      <c r="I7" s="49"/>
-      <c r="J7" s="50"/>
+      <c r="B7" s="48"/>
+      <c r="C7" s="48"/>
+      <c r="D7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="48"/>
+      <c r="G7" s="48"/>
+      <c r="H7" s="48"/>
+      <c r="I7" s="48"/>
+      <c r="J7" s="49"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="51" t="s">
+      <c r="A8" s="50" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="52"/>
-      <c r="C8" s="52"/>
-      <c r="D8" s="52"/>
-      <c r="E8" s="52"/>
-      <c r="F8" s="52"/>
-      <c r="G8" s="52"/>
-      <c r="H8" s="52"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="53"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
+      <c r="J8" s="46"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="48" t="s">
+      <c r="A9" s="47" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="49"/>
-      <c r="C9" s="49"/>
-      <c r="D9" s="49"/>
-      <c r="E9" s="49"/>
-      <c r="F9" s="49"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="49"/>
-      <c r="I9" s="49"/>
-      <c r="J9" s="50"/>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
+      <c r="H9" s="48"/>
+      <c r="I9" s="48"/>
+      <c r="J9" s="49"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2384,17 +2386,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="54" t="s">
+      <c r="C10" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="55"/>
+      <c r="D10" s="52"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="44" t="s">
+      <c r="F10" s="53" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="46"/>
+      <c r="G10" s="54"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2412,15 +2414,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="35" t="s">
+      <c r="C11" s="63" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="36"/>
+      <c r="D11" s="64"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="33" t="s">
+      <c r="F11" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="37"/>
+      <c r="G11" s="65"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2430,82 +2432,65 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="38" t="s">
+      <c r="A12" s="66" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="39"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="39"/>
-      <c r="E12" s="39"/>
-      <c r="F12" s="39"/>
-      <c r="G12" s="39"/>
-      <c r="H12" s="39"/>
-      <c r="I12" s="39"/>
-      <c r="J12" s="40"/>
+      <c r="B12" s="67"/>
+      <c r="C12" s="67"/>
+      <c r="D12" s="67"/>
+      <c r="E12" s="67"/>
+      <c r="F12" s="67"/>
+      <c r="G12" s="67"/>
+      <c r="H12" s="67"/>
+      <c r="I12" s="67"/>
+      <c r="J12" s="68"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="41" t="s">
+      <c r="B13" s="69" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="43"/>
-      <c r="E13" s="44" t="s">
+      <c r="C13" s="70"/>
+      <c r="D13" s="71"/>
+      <c r="E13" s="53" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="45"/>
-      <c r="G13" s="46"/>
+      <c r="F13" s="72"/>
+      <c r="G13" s="54"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="44" t="s">
+      <c r="I13" s="53" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="47"/>
+      <c r="J13" s="73"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="55" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="28"/>
-      <c r="D14" s="29"/>
-      <c r="E14" s="30" t="s">
+      <c r="C14" s="56"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="58" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="31"/>
-      <c r="G14" s="32"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="60"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="33" t="s">
+      <c r="I14" s="61" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="34"/>
+      <c r="J14" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="26">
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2515,6 +2500,23 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">

--- a/daily_report.xlsx
+++ b/daily_report.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\软通文件\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D7A69E9-2573-4E26-ABE8-192B0C1B2AC1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B01C24CE-3762-457C-A31E-7446CB880AE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" tabRatio="875" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -485,19 +485,18 @@
   </si>
   <si>
     <t>重点工作: 
+1. 协助解决专线接入点资源不足的情况
+2. 对新业务系统的虚拟机
+重大风险: 无 
+周边求助: 无</t>
+    <phoneticPr fontId="30" type="noConversion"/>
+  </si>
+  <si>
+    <t>重点工作: 
 1. 联通机房蒙能云平台操作
 重大风险: 无 
 周边求助: 无
-周四: 在运营面测试创建obs和sfs 以及发放redis实例等操作</t>
-    <phoneticPr fontId="30" type="noConversion"/>
-  </si>
-  <si>
-    <t>重点工作: 
-1. 解决obs对象存储创建时权限不足问题
-2. sfs文件系统无法创建 参数报错问题
-3. 理解sentinel集群的作用及如何发放redis实例等操作
-重大风险: 无 
-周边求助: 无</t>
+周五: 办公室写方案</t>
     <phoneticPr fontId="30" type="noConversion"/>
   </si>
 </sst>
@@ -1267,37 +1266,105 @@
     <xf numFmtId="0" fontId="15" fillId="7" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="34" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="34" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
@@ -1324,93 +1391,25 @@
     <xf numFmtId="0" fontId="35" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="7" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="31" fillId="3" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="9" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="3" borderId="5" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="165" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="4" fillId="2" borderId="11" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="32" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="177" fontId="1" fillId="2" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -2149,7 +2148,7 @@
     </row>
     <row r="3" spans="1:8" ht="114" customHeight="1">
       <c r="A3" s="21" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B3" s="22"/>
       <c r="C3" s="22"/>
@@ -2173,7 +2172,7 @@
     </row>
     <row r="5" spans="1:8" ht="90" customHeight="1">
       <c r="A5" s="24" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B5" s="25"/>
       <c r="C5" s="25"/>
@@ -2230,154 +2229,154 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" ht="27.75">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="67" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="29"/>
+      <c r="B1" s="68"/>
+      <c r="C1" s="68"/>
+      <c r="D1" s="68"/>
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="68"/>
+      <c r="H1" s="68"/>
+      <c r="I1" s="68"/>
+      <c r="J1" s="69"/>
     </row>
     <row r="2" spans="1:11" ht="35" customHeight="1">
       <c r="A2" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="58" t="s">
         <v>31</v>
       </c>
-      <c r="C2" s="31"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="13" t="s">
         <v>26</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="58" t="s">
         <v>32</v>
       </c>
-      <c r="F2" s="31"/>
+      <c r="F2" s="59"/>
       <c r="G2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="H2" s="31" t="s">
+      <c r="H2" s="59" t="s">
         <v>36</v>
       </c>
-      <c r="I2" s="31"/>
-      <c r="J2" s="32"/>
+      <c r="I2" s="59"/>
+      <c r="J2" s="70"/>
       <c r="K2" s="9"/>
     </row>
     <row r="3" spans="1:11" ht="15.75">
       <c r="A3" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30" t="s">
+      <c r="B3" s="58" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="31"/>
-      <c r="D3" s="31"/>
-      <c r="E3" s="31"/>
-      <c r="F3" s="33" t="s">
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="57" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="33"/>
-      <c r="H3" s="34" t="s">
+      <c r="G3" s="57"/>
+      <c r="H3" s="71" t="s">
         <v>4</v>
       </c>
-      <c r="I3" s="35"/>
-      <c r="J3" s="36"/>
+      <c r="I3" s="72"/>
+      <c r="J3" s="73"/>
     </row>
     <row r="4" spans="1:11" ht="15.75">
-      <c r="A4" s="37" t="s">
+      <c r="A4" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="B4" s="33"/>
-      <c r="C4" s="33"/>
-      <c r="D4" s="33"/>
-      <c r="E4" s="33"/>
-      <c r="F4" s="30" t="s">
+      <c r="B4" s="57"/>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="58" t="s">
         <v>29</v>
       </c>
-      <c r="G4" s="31"/>
-      <c r="H4" s="38" t="s">
+      <c r="G4" s="59"/>
+      <c r="H4" s="60" t="s">
         <v>30</v>
       </c>
-      <c r="I4" s="39"/>
-      <c r="J4" s="40"/>
+      <c r="I4" s="61"/>
+      <c r="J4" s="62"/>
     </row>
     <row r="5" spans="1:11" ht="20.25">
-      <c r="A5" s="41" t="s">
+      <c r="A5" s="63" t="s">
         <v>34</v>
       </c>
-      <c r="B5" s="42"/>
-      <c r="C5" s="42"/>
-      <c r="D5" s="42"/>
-      <c r="E5" s="42"/>
-      <c r="F5" s="42"/>
-      <c r="G5" s="42"/>
-      <c r="H5" s="42"/>
-      <c r="I5" s="42"/>
-      <c r="J5" s="43"/>
+      <c r="B5" s="64"/>
+      <c r="C5" s="64"/>
+      <c r="D5" s="64"/>
+      <c r="E5" s="64"/>
+      <c r="F5" s="64"/>
+      <c r="G5" s="64"/>
+      <c r="H5" s="64"/>
+      <c r="I5" s="64"/>
+      <c r="J5" s="65"/>
     </row>
     <row r="6" spans="1:11" ht="353" customHeight="1">
-      <c r="A6" s="44" t="s">
+      <c r="A6" s="66" t="s">
         <v>38</v>
       </c>
-      <c r="B6" s="45"/>
-      <c r="C6" s="45"/>
-      <c r="D6" s="45"/>
-      <c r="E6" s="45"/>
-      <c r="F6" s="45"/>
-      <c r="G6" s="45"/>
-      <c r="H6" s="45"/>
-      <c r="I6" s="45"/>
-      <c r="J6" s="46"/>
+      <c r="B6" s="52"/>
+      <c r="C6" s="52"/>
+      <c r="D6" s="52"/>
+      <c r="E6" s="52"/>
+      <c r="F6" s="52"/>
+      <c r="G6" s="52"/>
+      <c r="H6" s="52"/>
+      <c r="I6" s="52"/>
+      <c r="J6" s="53"/>
       <c r="K6" s="14" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="7" spans="1:11" ht="20.25">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="48" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="48"/>
-      <c r="I7" s="48"/>
-      <c r="J7" s="49"/>
+      <c r="B7" s="49"/>
+      <c r="C7" s="49"/>
+      <c r="D7" s="49"/>
+      <c r="E7" s="49"/>
+      <c r="F7" s="49"/>
+      <c r="G7" s="49"/>
+      <c r="H7" s="49"/>
+      <c r="I7" s="49"/>
+      <c r="J7" s="50"/>
     </row>
     <row r="8" spans="1:11" ht="32" customHeight="1">
-      <c r="A8" s="50" t="s">
+      <c r="A8" s="51" t="s">
         <v>35</v>
       </c>
-      <c r="B8" s="45"/>
-      <c r="C8" s="45"/>
-      <c r="D8" s="45"/>
-      <c r="E8" s="45"/>
-      <c r="F8" s="45"/>
-      <c r="G8" s="45"/>
-      <c r="H8" s="45"/>
-      <c r="I8" s="45"/>
-      <c r="J8" s="46"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
+      <c r="D8" s="52"/>
+      <c r="E8" s="52"/>
+      <c r="F8" s="52"/>
+      <c r="G8" s="52"/>
+      <c r="H8" s="52"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="53"/>
     </row>
     <row r="9" spans="1:11" ht="20.25">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="48" t="s">
         <v>7</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
-      <c r="H9" s="48"/>
-      <c r="I9" s="48"/>
-      <c r="J9" s="49"/>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
+      <c r="H9" s="49"/>
+      <c r="I9" s="49"/>
+      <c r="J9" s="50"/>
     </row>
     <row r="10" spans="1:11" ht="29.25">
       <c r="A10" s="2" t="s">
@@ -2386,17 +2385,17 @@
       <c r="B10" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="51" t="s">
+      <c r="C10" s="54" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="52"/>
+      <c r="D10" s="55"/>
       <c r="E10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="F10" s="53" t="s">
+      <c r="F10" s="44" t="s">
         <v>12</v>
       </c>
-      <c r="G10" s="54"/>
+      <c r="G10" s="46"/>
       <c r="H10" s="4" t="s">
         <v>13</v>
       </c>
@@ -2414,15 +2413,15 @@
       <c r="B11" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="63" t="s">
+      <c r="C11" s="35" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="64"/>
+      <c r="D11" s="36"/>
       <c r="E11" s="7"/>
-      <c r="F11" s="61" t="s">
+      <c r="F11" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="G11" s="65"/>
+      <c r="G11" s="37"/>
       <c r="H11" s="8" t="s">
         <v>16</v>
       </c>
@@ -2432,65 +2431,82 @@
       </c>
     </row>
     <row r="12" spans="1:11" ht="14" customHeight="1">
-      <c r="A12" s="66" t="s">
+      <c r="A12" s="38" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="67"/>
-      <c r="C12" s="67"/>
-      <c r="D12" s="67"/>
-      <c r="E12" s="67"/>
-      <c r="F12" s="67"/>
-      <c r="G12" s="67"/>
-      <c r="H12" s="67"/>
-      <c r="I12" s="67"/>
-      <c r="J12" s="68"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="39"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="39"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="39"/>
+      <c r="H12" s="39"/>
+      <c r="I12" s="39"/>
+      <c r="J12" s="40"/>
     </row>
     <row r="13" spans="1:11" ht="14" customHeight="1">
       <c r="A13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B13" s="69" t="s">
+      <c r="B13" s="41" t="s">
         <v>18</v>
       </c>
-      <c r="C13" s="70"/>
-      <c r="D13" s="71"/>
-      <c r="E13" s="53" t="s">
+      <c r="C13" s="42"/>
+      <c r="D13" s="43"/>
+      <c r="E13" s="44" t="s">
         <v>19</v>
       </c>
-      <c r="F13" s="72"/>
-      <c r="G13" s="54"/>
+      <c r="F13" s="45"/>
+      <c r="G13" s="46"/>
       <c r="H13" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="I13" s="53" t="s">
+      <c r="I13" s="44" t="s">
         <v>21</v>
       </c>
-      <c r="J13" s="73"/>
+      <c r="J13" s="47"/>
     </row>
     <row r="14" spans="1:11" ht="14" customHeight="1">
       <c r="A14" s="5">
         <v>1</v>
       </c>
-      <c r="B14" s="55" t="s">
+      <c r="B14" s="27" t="s">
         <v>23</v>
       </c>
-      <c r="C14" s="56"/>
-      <c r="D14" s="57"/>
-      <c r="E14" s="58" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="29"/>
+      <c r="E14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="59"/>
-      <c r="G14" s="60"/>
+      <c r="F14" s="31"/>
+      <c r="G14" s="32"/>
       <c r="H14" s="8" t="s">
         <v>16</v>
       </c>
-      <c r="I14" s="61" t="s">
+      <c r="I14" s="33" t="s">
         <v>16</v>
       </c>
-      <c r="J14" s="62"/>
+      <c r="J14" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="26">
+    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="B2:C2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="H2:J2"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="A4:E4"/>
+    <mergeCell ref="F4:G4"/>
+    <mergeCell ref="H4:J4"/>
+    <mergeCell ref="A5:J5"/>
+    <mergeCell ref="A6:J6"/>
+    <mergeCell ref="A7:J7"/>
+    <mergeCell ref="A8:J8"/>
+    <mergeCell ref="A9:J9"/>
+    <mergeCell ref="C10:D10"/>
+    <mergeCell ref="F10:G10"/>
     <mergeCell ref="B14:D14"/>
     <mergeCell ref="E14:G14"/>
     <mergeCell ref="I14:J14"/>
@@ -2500,23 +2516,6 @@
     <mergeCell ref="B13:D13"/>
     <mergeCell ref="E13:G13"/>
     <mergeCell ref="I13:J13"/>
-    <mergeCell ref="A7:J7"/>
-    <mergeCell ref="A8:J8"/>
-    <mergeCell ref="A9:J9"/>
-    <mergeCell ref="C10:D10"/>
-    <mergeCell ref="F10:G10"/>
-    <mergeCell ref="A4:E4"/>
-    <mergeCell ref="F4:G4"/>
-    <mergeCell ref="H4:J4"/>
-    <mergeCell ref="A5:J5"/>
-    <mergeCell ref="A6:J6"/>
-    <mergeCell ref="A1:J1"/>
-    <mergeCell ref="B2:C2"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="H2:J2"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:J3"/>
   </mergeCells>
   <phoneticPr fontId="30" type="noConversion"/>
   <dataValidations count="2">
